--- a/docs/oc-regiones/administracion-y-entrega-de-beneficios/arica-y-parinacota.xlsx
+++ b/docs/oc-regiones/administracion-y-entrega-de-beneficios/arica-y-parinacota.xlsx
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>846.4299999999999</v>
+        <v>839.26</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>21811.88</v>
+        <v>21699.81</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>3056.54</v>
+        <v>3067.45</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>2726.29</v>
+        <v>2773.35</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>46870.47</v>
+        <v>47195.17</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>47154.93</v>
+        <v>47374.54</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>2244.07</v>
+        <v>2254.52</v>
       </c>
     </row>
     <row r="9">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>341.99</v>
+        <v>343.58</v>
       </c>
     </row>
     <row r="10">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>18614.19</v>
+        <v>18537.48</v>
       </c>
     </row>
     <row r="11">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>23715.7</v>
+        <v>23409.16</v>
       </c>
     </row>
     <row r="12">
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>354.63</v>
+        <v>350.05</v>
       </c>
     </row>
     <row r="13">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>1702.75</v>
+        <v>1696.65</v>
       </c>
     </row>
     <row r="14">
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>3453.54</v>
+        <v>3413.57</v>
       </c>
     </row>
     <row r="15">
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>3274.53</v>
+        <v>3246.79</v>
       </c>
     </row>
     <row r="16">
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>45500.64</v>
+        <v>45813.83</v>
       </c>
     </row>
     <row r="17">
@@ -1484,7 +1484,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>2443.01</v>
+        <v>2463.89</v>
       </c>
     </row>
     <row r="18">
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>16968.39</v>
+        <v>16535.09</v>
       </c>
     </row>
     <row r="19">
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>543.01</v>
+        <v>535.22</v>
       </c>
     </row>
     <row r="20">
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>15984.78</v>
+        <v>15900.34</v>
       </c>
     </row>
     <row r="21">
@@ -1728,7 +1728,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>30100.8</v>
+        <v>29912.17</v>
       </c>
     </row>
     <row r="22">
@@ -1789,7 +1789,7 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>16968.39</v>
+        <v>17226.72</v>
       </c>
     </row>
     <row r="23">
@@ -1850,7 +1850,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>389.16</v>
+        <v>398.62</v>
       </c>
     </row>
     <row r="24">
@@ -1911,7 +1911,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>45785.81</v>
+        <v>46943.28</v>
       </c>
     </row>
     <row r="25">
@@ -1972,7 +1972,7 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>28138.41</v>
+        <v>28255.43</v>
       </c>
     </row>
     <row r="26">
@@ -2033,7 +2033,7 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>3480.2</v>
+        <v>3454.15</v>
       </c>
     </row>
     <row r="27">
@@ -2094,7 +2094,7 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>11119.59</v>
+        <v>11036.37</v>
       </c>
     </row>
     <row r="28">
@@ -2159,7 +2159,7 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>242167.23</v>
+        <v>243421.02</v>
       </c>
     </row>
     <row r="29">
@@ -2220,7 +2220,7 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>50380.79</v>
+        <v>50429.35</v>
       </c>
     </row>
     <row r="30">
@@ -2281,7 +2281,7 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>27035.37</v>
+        <v>28229.31</v>
       </c>
     </row>
     <row r="31">
@@ -2342,7 +2342,7 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>1769.44</v>
+        <v>1820.83</v>
       </c>
     </row>
     <row r="32">
@@ -2403,7 +2403,7 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>3297.09</v>
+        <v>3351.43</v>
       </c>
     </row>
     <row r="33">
@@ -2464,7 +2464,7 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>189.03</v>
+        <v>186.6</v>
       </c>
     </row>
     <row r="34">
@@ -2525,7 +2525,7 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>20329.67</v>
+        <v>20186.21</v>
       </c>
     </row>
     <row r="35">
@@ -2586,7 +2586,7 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>729.76</v>
+        <v>718.87</v>
       </c>
     </row>
     <row r="36">
@@ -2647,7 +2647,7 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>3622.23</v>
+        <v>3599.02</v>
       </c>
     </row>
     <row r="37">
@@ -2708,7 +2708,7 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>1002.32</v>
+        <v>987.8200000000001</v>
       </c>
     </row>
     <row r="38">
@@ -2769,7 +2769,7 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>196.02</v>
+        <v>189.77</v>
       </c>
     </row>
     <row r="39">
@@ -2830,7 +2830,7 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>26000.29</v>
+        <v>25487.53</v>
       </c>
     </row>
     <row r="40">
@@ -2891,7 +2891,7 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>50288.67</v>
+        <v>49296.9</v>
       </c>
     </row>
     <row r="41">
@@ -2952,7 +2952,7 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>12857.73</v>
+        <v>12519.15</v>
       </c>
     </row>
     <row r="42">
@@ -3013,7 +3013,7 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>3341.18</v>
+        <v>3355.07</v>
       </c>
     </row>
     <row r="43">
@@ -3074,7 +3074,7 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>196.02</v>
+        <v>195.17</v>
       </c>
     </row>
     <row r="44">
@@ -3135,7 +3135,7 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>27797.9</v>
+        <v>27678.48</v>
       </c>
     </row>
     <row r="45">
@@ -3196,7 +3196,7 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>3899.12</v>
+        <v>3913.89</v>
       </c>
     </row>
     <row r="46">
@@ -3257,7 +3257,7 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>51361.14</v>
+        <v>51231.46</v>
       </c>
     </row>
     <row r="47">
@@ -3318,7 +3318,7 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>334.21</v>
+        <v>337.39</v>
       </c>
     </row>
     <row r="48">
@@ -3379,7 +3379,7 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>392.14</v>
+        <v>390.42</v>
       </c>
     </row>
     <row r="49">
@@ -3444,7 +3444,7 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>1146290.69</v>
+        <v>1143688.83</v>
       </c>
     </row>
     <row r="50">
@@ -3505,7 +3505,7 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>77693.41</v>
+        <v>78075.06</v>
       </c>
     </row>
     <row r="51">
@@ -3566,7 +3566,7 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>29025.85</v>
+        <v>29122.13</v>
       </c>
     </row>
     <row r="52">
@@ -3627,7 +3627,7 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>77199.2</v>
+        <v>78303.85000000001</v>
       </c>
     </row>
     <row r="53">
@@ -3688,7 +3688,7 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>1375.04</v>
+        <v>1389.02</v>
       </c>
     </row>
     <row r="54">
@@ -3749,7 +3749,7 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>75.72</v>
+        <v>76.06</v>
       </c>
     </row>
     <row r="55">
@@ -3810,7 +3810,7 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>1240.11</v>
+        <v>1268.08</v>
       </c>
     </row>
     <row r="56">
@@ -3871,7 +3871,7 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>836.85</v>
+        <v>855.73</v>
       </c>
     </row>
     <row r="57">
@@ -3932,7 +3932,7 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>30169.39</v>
+        <v>30455.97</v>
       </c>
     </row>
     <row r="58">
@@ -3993,7 +3993,7 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>612.26</v>
+        <v>614.65</v>
       </c>
     </row>
     <row r="59">
@@ -4058,7 +4058,7 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>739819.76</v>
+        <v>742699.71</v>
       </c>
     </row>
     <row r="60">
@@ -4119,7 +4119,7 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>27039.54</v>
+        <v>27228.77</v>
       </c>
     </row>
     <row r="61">
@@ -4180,7 +4180,7 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>10271.91</v>
+        <v>10343.8</v>
       </c>
     </row>
     <row r="62">
@@ -4241,7 +4241,7 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>15298.58</v>
+        <v>15267.91</v>
       </c>
     </row>
     <row r="63">
@@ -4302,7 +4302,7 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>35883.54</v>
+        <v>35304.47</v>
       </c>
     </row>
     <row r="64">
@@ -4363,7 +4363,7 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>1826.05</v>
+        <v>1796.58</v>
       </c>
     </row>
     <row r="65">
@@ -4424,7 +4424,7 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>857.17</v>
+        <v>852.96</v>
       </c>
     </row>
     <row r="66">
@@ -4485,7 +4485,7 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>429.66</v>
+        <v>432.54</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/administracion-y-entrega-de-beneficios/arica-y-parinacota.xlsx
+++ b/docs/oc-regiones/administracion-y-entrega-de-beneficios/arica-y-parinacota.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M66"/>
+  <dimension ref="A1:M70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1606-502-CM25</t>
+          <t>3483-42-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -524,12 +524,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-03-07</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -539,12 +539,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>60.108.000-1</t>
+          <t>65.286.830-4</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>AGENCIA CHILENA DE COOPERACION INTERNACIONAL PARA EL DESARROLLO</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>839.26</v>
+        <v>1926.56</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1079596-334-CM25</t>
+          <t>3340-152-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -585,12 +585,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-05-20</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -600,12 +600,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>60.505.101-4</t>
+          <t>65.286.850-9</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XV ZONA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -630,13 +630,13 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>21699.81</v>
+        <v>639.66</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>3459-303-CM25</t>
+          <t>707409-60-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -646,12 +646,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-06-09</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -661,12 +661,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>65.287.570-K</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -691,13 +691,13 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>3067.45</v>
+        <v>217.37</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>5360-424-CM25</t>
+          <t>5702-722-CM25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -707,27 +707,27 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>70.770.800-k</t>
+          <t>61.979.020-0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>2773.35</v>
+        <v>15812.72</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>521473-22-CM25</t>
+          <t>1606-502-CM25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -773,22 +773,22 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>70.770.800-k</t>
+          <t>60.108.000-1</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>AGENCIA CHILENA DE COOPERACION INTERNACIONAL PARA EL DESARROLLO</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -813,13 +813,13 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>47195.17</v>
+        <v>839.26</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>635-4846-CM25</t>
+          <t>1079596-334-CM25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -844,12 +844,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>61.606.000-7</t>
+          <t>60.505.101-4</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DE ARICA Y PARINACOTA</t>
+          <t>SECCIÓN COMPRAS XV ZONA</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -874,13 +874,13 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>47374.54</v>
+        <v>21699.81</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>696027-106-CM25</t>
+          <t>3459-303-CM25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -905,12 +905,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>61.935.400-1</t>
+          <t>65.287.570-K</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>MINISTERIO PUBLICO</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -935,13 +935,13 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>2254.52</v>
+        <v>3067.45</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>696027-107-CM25</t>
+          <t>5360-424-CM25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -956,22 +956,22 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>61.935.400-1</t>
+          <t>70.770.800-k</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>MINISTERIO PUBLICO</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -996,13 +996,13 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>343.58</v>
+        <v>2773.35</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>5360-435-CM25</t>
+          <t>521473-22-CM25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1017,7 +1017,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1057,13 +1057,13 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>18537.48</v>
+        <v>47195.17</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>1079596-385-CM25</t>
+          <t>635-4846-CM25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1073,12 +1073,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>60.505.101-4</t>
+          <t>61.606.000-7</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XV ZONA</t>
+          <t>SERVICIO DE SALUD DE ARICA Y PARINACOTA</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1118,13 +1118,13 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>23409.16</v>
+        <v>47374.54</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>1079596-389-CM25</t>
+          <t>696027-107-CM25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1134,12 +1134,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1149,12 +1149,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>60.505.101-4</t>
+          <t>61.935.400-1</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XV ZONA</t>
+          <t>MINISTERIO PUBLICO</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1179,13 +1179,13 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>350.05</v>
+        <v>343.58</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>3459-313-CM25</t>
+          <t>696027-106-CM25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1195,12 +1195,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1210,12 +1210,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>65.287.570-K</t>
+          <t>61.935.400-1</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>MINISTERIO PUBLICO</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1240,13 +1240,13 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>1696.65</v>
+        <v>2254.52</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>3483-275-CM25</t>
+          <t>5360-435-CM25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1256,27 +1256,27 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>65.286.830-4</t>
+          <t>70.770.800-k</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1301,13 +1301,13 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>3413.57</v>
+        <v>18537.48</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>3483-282-CM25</t>
+          <t>1079596-389-CM25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1332,12 +1332,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>65.286.830-4</t>
+          <t>60.505.101-4</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>SECCIÓN COMPRAS XV ZONA</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1362,13 +1362,13 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>3246.79</v>
+        <v>350.05</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>635-5043-CM25</t>
+          <t>1079596-385-CM25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1393,12 +1393,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>61.606.000-7</t>
+          <t>60.505.101-4</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DE ARICA Y PARINACOTA</t>
+          <t>SECCIÓN COMPRAS XV ZONA</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1423,13 +1423,13 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>45813.83</v>
+        <v>23409.16</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>1079596-418-CM25</t>
+          <t>3459-313-CM25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1444,7 +1444,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>60.505.101-4</t>
+          <t>65.287.570-K</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XV ZONA</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1484,13 +1484,13 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>2463.89</v>
+        <v>1696.65</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>5702-1-CM26</t>
+          <t>3483-275-CM25</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1515,12 +1515,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>61.979.020-0</t>
+          <t>65.286.830-4</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Direc.Reg.Arica y Parinacota</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1545,13 +1545,13 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>16535.09</v>
+        <v>3413.57</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>707409-3-CM26</t>
+          <t>3483-282-CM25</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1561,12 +1561,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1576,12 +1576,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>65.286.830-4</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1606,13 +1606,13 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>535.22</v>
+        <v>3246.79</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>576152-1-CM26</t>
+          <t>635-5043-CM25</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1622,27 +1622,27 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>61.002.002-k</t>
+          <t>61.606.000-7</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>SERVICIO DE BIENESTAR  DEL  SRCEI</t>
+          <t>SERVICIO DE SALUD DE ARICA Y PARINACOTA</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1667,13 +1667,13 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>15900.34</v>
+        <v>45813.83</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>1079596-5-CM26</t>
+          <t>1079596-418-CM25</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1683,12 +1683,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1728,13 +1728,13 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>29912.17</v>
+        <v>2463.89</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>5702-26-CM26</t>
+          <t>5702-1-CM26</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1749,7 +1749,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1789,13 +1789,13 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>17226.72</v>
+        <v>16535.09</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>3483-13-CM26</t>
+          <t>707409-3-CM26</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1810,7 +1810,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1820,12 +1820,12 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>65.286.830-4</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1850,13 +1850,13 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>398.62</v>
+        <v>535.22</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>635-60-CM26</t>
+          <t>576152-1-CM26</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1871,22 +1871,22 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>61.606.000-7</t>
+          <t>61.002.002-k</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DE ARICA Y PARINACOTA</t>
+          <t>SERVICIO DE BIENESTAR  DEL  SRCEI</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1911,13 +1911,13 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>46943.28</v>
+        <v>15900.34</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>1079596-19-CM26</t>
+          <t>1079596-5-CM26</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1927,12 +1927,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1972,13 +1972,13 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>28255.43</v>
+        <v>29912.17</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>3483-3-CM26</t>
+          <t>5702-26-CM26</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1988,12 +1988,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2003,12 +2003,12 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>65.286.830-4</t>
+          <t>61.979.020-0</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>Direc.Reg.Arica y Parinacota</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2033,13 +2033,13 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>3454.15</v>
+        <v>17226.72</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>5360-48-CM26</t>
+          <t>3483-13-CM26</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2049,27 +2049,27 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>70.770.800-k</t>
+          <t>65.286.830-4</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2094,13 +2094,13 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>11036.37</v>
+        <v>398.62</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2021-8-CM26</t>
+          <t>635-60-CM26</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2110,12 +2110,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2125,12 +2125,12 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>61.101.040-0</t>
+          <t>61.606.000-7</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Estado Mayor Conjunto</t>
+          <t>SERVICIO DE SALUD DE ARICA Y PARINACOTA</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2148,24 +2148,20 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
+      <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>243421.02</v>
+        <v>46943.28</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>635-197-CM26</t>
+          <t>1079596-19-CM26</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2180,7 +2176,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2190,12 +2186,12 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>61.606.000-7</t>
+          <t>60.505.101-4</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DE ARICA Y PARINACOTA</t>
+          <t>SECCIÓN COMPRAS XV ZONA</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2220,13 +2216,13 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>50429.35</v>
+        <v>28255.43</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>1079596-30-CM26</t>
+          <t>3483-3-CM26</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2236,12 +2232,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2251,12 +2247,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>60.505.101-4</t>
+          <t>65.286.830-4</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XV ZONA</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2281,13 +2277,13 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>28229.31</v>
+        <v>3454.15</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>3483-52-CM26</t>
+          <t>5360-48-CM26</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2297,27 +2293,27 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>65.286.830-4</t>
+          <t>70.770.800-k</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2342,13 +2338,13 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>1820.83</v>
+        <v>11036.37</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>3483-70-CM26</t>
+          <t>2021-8-CM26</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2358,12 +2354,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2373,12 +2369,12 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>65.286.830-4</t>
+          <t>61.101.040-0</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>Estado Mayor Conjunto</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2396,20 +2392,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>3351.43</v>
+        <v>243421.02</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>3483-64-CM26</t>
+          <t>635-197-CM26</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2419,12 +2419,12 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2434,12 +2434,12 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>65.286.830-4</t>
+          <t>61.606.000-7</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>SERVICIO DE SALUD DE ARICA Y PARINACOTA</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2464,13 +2464,13 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>186.6</v>
+        <v>50429.35</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>5360-78-CM26</t>
+          <t>1079596-30-CM26</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2485,22 +2485,22 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>70.770.800-k</t>
+          <t>60.505.101-4</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>SECCIÓN COMPRAS XV ZONA</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2525,13 +2525,13 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>20186.21</v>
+        <v>28229.31</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>707409-32-CM26</t>
+          <t>3483-52-CM26</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2546,7 +2546,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2556,12 +2556,12 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>65.286.830-4</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2586,13 +2586,13 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>718.87</v>
+        <v>1820.83</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>707409-34-CM26</t>
+          <t>3483-70-CM26</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2607,7 +2607,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2617,12 +2617,12 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>65.286.830-4</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2647,13 +2647,13 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>3599.02</v>
+        <v>3351.43</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>1079596-47-CM26</t>
+          <t>3483-64-CM26</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2668,7 +2668,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2678,12 +2678,12 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>60.505.101-4</t>
+          <t>65.286.830-4</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XV ZONA</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2708,13 +2708,13 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>987.8200000000001</v>
+        <v>186.6</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>3483-111-CM26</t>
+          <t>5360-78-CM26</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2724,27 +2724,27 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>65.286.830-4</t>
+          <t>70.770.800-k</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2769,13 +2769,13 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>189.77</v>
+        <v>20186.21</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>1079596-52-CM26</t>
+          <t>707409-32-CM26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2785,12 +2785,12 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2800,12 +2800,12 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>60.505.101-4</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XV ZONA</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2830,13 +2830,13 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>25487.53</v>
+        <v>718.87</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>635-376-CM26</t>
+          <t>707409-34-CM26</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>61.606.000-7</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DE ARICA Y PARINACOTA</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2891,13 +2891,13 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>49296.9</v>
+        <v>3599.02</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>5360-87-CM26</t>
+          <t>1079596-47-CM26</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2907,27 +2907,27 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>70.770.800-k</t>
+          <t>60.505.101-4</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>SECCIÓN COMPRAS XV ZONA</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2952,13 +2952,13 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>12519.15</v>
+        <v>987.8200000000001</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>3483-117-CM26</t>
+          <t>3483-111-CM26</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2973,7 +2973,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -3013,13 +3013,13 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>3355.07</v>
+        <v>189.77</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>3483-166-CM26</t>
+          <t>1079596-52-CM26</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3034,7 +3034,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -3044,12 +3044,12 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>65.286.830-4</t>
+          <t>60.505.101-4</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>SECCIÓN COMPRAS XV ZONA</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3074,13 +3074,13 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>195.17</v>
+        <v>25487.53</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>1079596-71-CM26</t>
+          <t>635-376-CM26</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -3105,12 +3105,12 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>60.505.101-4</t>
+          <t>61.606.000-7</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XV ZONA</t>
+          <t>SERVICIO DE SALUD DE ARICA Y PARINACOTA</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3135,13 +3135,13 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>27678.48</v>
+        <v>49296.9</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>3483-170-CM26</t>
+          <t>5360-87-CM26</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3151,27 +3151,27 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>65.286.830-4</t>
+          <t>70.770.800-k</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3196,13 +3196,13 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>3913.89</v>
+        <v>12519.15</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>635-553-CM26</t>
+          <t>3483-117-CM26</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3212,12 +3212,12 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -3227,12 +3227,12 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>61.606.000-7</t>
+          <t>65.286.830-4</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DE ARICA Y PARINACOTA</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3257,13 +3257,13 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>51231.46</v>
+        <v>3355.07</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>3459-114-CM26</t>
+          <t>3483-166-CM26</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3273,12 +3273,12 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -3288,7 +3288,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>65.287.570-K</t>
+          <t>65.286.830-4</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -3318,13 +3318,13 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>337.39</v>
+        <v>195.17</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>3483-192-CM26</t>
+          <t>1079596-71-CM26</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3334,12 +3334,12 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -3349,12 +3349,12 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>65.286.830-4</t>
+          <t>60.505.101-4</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>SECCIÓN COMPRAS XV ZONA</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3379,13 +3379,13 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>390.42</v>
+        <v>27678.48</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>635-602-SE26</t>
+          <t>3483-170-CM26</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3400,7 +3400,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -3410,12 +3410,12 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>61.606.000-7</t>
+          <t>65.286.830-4</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DE ARICA Y PARINACOTA</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -3433,24 +3433,20 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
+      <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>1143688.83</v>
+        <v>3913.89</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>1075963-6467-CM26</t>
+          <t>635-553-CM26</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3465,7 +3461,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -3475,12 +3471,12 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>61.606.000-7</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>SERVICIO DE SALUD DE ARICA Y PARINACOTA</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -3505,13 +3501,13 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>78075.06</v>
+        <v>51231.46</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>1079596-95-CM26</t>
+          <t>3459-114-CM26</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3526,7 +3522,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -3536,12 +3532,12 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>60.505.101-4</t>
+          <t>65.287.570-K</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XV ZONA</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -3566,13 +3562,13 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>29122.13</v>
+        <v>337.39</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>1075963-6468-CM26</t>
+          <t>3483-192-CM26</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3582,12 +3578,12 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -3597,12 +3593,12 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>65.286.830-4</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -3627,13 +3623,13 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>78303.85000000001</v>
+        <v>390.42</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>941739-43-CM26</t>
+          <t>635-602-SE26</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3643,27 +3639,27 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>70.770.800-K</t>
+          <t>61.606.000-7</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>SERVICIO DE SALUD DE ARICA Y PARINACOTA</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -3681,20 +3677,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
       <c r="L53" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>1389.02</v>
+        <v>1143688.83</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>1079596-106-CM26</t>
+          <t>1075963-6467-CM26</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3704,12 +3704,12 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3719,12 +3719,12 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>60.505.101-4</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XV ZONA</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3749,13 +3749,13 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>76.06</v>
+        <v>78075.06</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>1337362-34-CM26</t>
+          <t>1079596-95-CM26</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -3780,12 +3780,12 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>60.905.000-4</t>
+          <t>60.505.101-4</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>DIRECCIÓN REGIONAL DE ARICA Y PARINACOTA</t>
+          <t>SECCIÓN COMPRAS XV ZONA</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3810,13 +3810,13 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>1268.08</v>
+        <v>29122.13</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>707409-61-CM26</t>
+          <t>1075963-6468-CM26</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3831,7 +3831,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -3841,12 +3841,12 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -3871,43 +3871,43 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>855.73</v>
+        <v>78303.85000000001</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>1079596-123-CM26</t>
+          <t>941739-43-CM26</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2239-1-LR26</t>
+          <t>2239-13-LR23</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>60.505.101-4</t>
+          <t>70.770.800-K</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XV ZONA</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -3932,43 +3932,43 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>30455.97</v>
+        <v>1389.02</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>1707-19-CM26</t>
+          <t>1079596-106-CM26</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2239-1-LR26</t>
+          <t>2239-13-LR23</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>60.511.139-4</t>
+          <t>60.505.101-4</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE PARINACOTA</t>
+          <t>SECCIÓN COMPRAS XV ZONA</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -3993,13 +3993,13 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>614.65</v>
+        <v>76.06</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>1075963-8976-SE26</t>
+          <t>1337362-34-CM26</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>60.905.000-4</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>DIRECCIÓN REGIONAL DE ARICA Y PARINACOTA</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4047,39 +4047,35 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
+      <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>742699.71</v>
+        <v>1268.08</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>3348-81-CM26</t>
+          <t>707409-61-CM26</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2239-1-LR26</t>
+          <t>2239-13-LR23</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -4089,12 +4085,12 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>61.101.082-6</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4119,13 +4115,13 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>27228.77</v>
+        <v>855.73</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>5593-115-CM26</t>
+          <t>1079596-123-CM26</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4140,7 +4136,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -4150,12 +4146,12 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>60.506.000-5</t>
+          <t>60.505.101-4</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
+          <t>SECCIÓN COMPRAS XV ZONA</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -4165,12 +4161,12 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>76.032.107-9</t>
+          <t>96.781.350-8</t>
         </is>
       </c>
       <c r="K61" t="inlineStr"/>
@@ -4180,13 +4176,13 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>10343.8</v>
+        <v>30455.97</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>5360-169-CM26</t>
+          <t>1707-19-CM26</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4201,7 +4197,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -4211,12 +4207,12 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>70.770.800-k</t>
+          <t>60.511.139-4</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE PARINACOTA</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -4241,18 +4237,18 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>15267.91</v>
+        <v>614.65</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>1572-76-CM26</t>
+          <t>1075963-8976-SE26</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2239-1-LR26</t>
+          <t>2239-13-LR23</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -4262,22 +4258,22 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -4295,20 +4291,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
       <c r="L63" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>35304.47</v>
+        <v>742699.71</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>1572-77-CM26</t>
+          <t>3348-81-CM26</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4323,22 +4323,22 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>61.101.082-6</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -4363,13 +4363,13 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>1796.58</v>
+        <v>27228.77</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>1093870-11-CM26</t>
+          <t>5593-115-CM26</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4384,22 +4384,22 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>65.184.303-0</t>
+          <t>60.506.000-5</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE EDUCACION SUPERIOR</t>
+          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -4409,12 +4409,12 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>96.781.350-8</t>
+          <t>76.032.107-9</t>
         </is>
       </c>
       <c r="K65" t="inlineStr"/>
@@ -4424,13 +4424,13 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>852.96</v>
+        <v>10343.8</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>5702-540-CM26</t>
+          <t>5360-169-CM26</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4445,7 +4445,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -4455,12 +4455,12 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>61.979.020-0</t>
+          <t>70.770.800-k</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Direc.Reg.Arica y Parinacota</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -4485,6 +4485,250 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
+        <v>15267.91</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>1572-76-CM26</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>70.072.600-2</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="n">
+        <v>35304.47</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>1572-77-CM26</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>70.072.600-2</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="n">
+        <v>1796.58</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>1093870-11-CM26</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>65.184.303-0</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>SUBSECRETARIA DE EDUCACION SUPERIOR</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="n">
+        <v>852.96</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>5702-540-CM26</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>61.979.020-0</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Direc.Reg.Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="n">
         <v>432.54</v>
       </c>
     </row>

--- a/docs/oc-regiones/administracion-y-entrega-de-beneficios/arica-y-parinacota.xlsx
+++ b/docs/oc-regiones/administracion-y-entrega-de-beneficios/arica-y-parinacota.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Arica y Parinacota" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Arica y Parinacota" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M70"/>
+  <dimension ref="A1:M134"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>3483-42-CM25</t>
+          <t>5702-17-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -524,12 +524,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>mar-2025</t>
+          <t>ene-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-03-07</t>
+          <t>2025-01-10</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -539,12 +539,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>65.286.830-4</t>
+          <t>61.979.020-0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>1926.56</v>
+        <v>39843.14</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>3340-152-CM25</t>
+          <t>3483-4-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -585,12 +585,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>may-2025</t>
+          <t>ene-2025</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-05-20</t>
+          <t>2025-01-23</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>65.286.850-9</t>
+          <t>65.286.830-4</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -630,13 +630,13 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>639.66</v>
+        <v>3416.33</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>707409-60-CM25</t>
+          <t>5593-17-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -646,12 +646,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>jun-2025</t>
+          <t>ene-2025</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025-06-09</t>
+          <t>2025-01-23</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -661,12 +661,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>60.506.000-5</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -691,13 +691,13 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>217.37</v>
+        <v>22105.67</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>5702-722-CM25</t>
+          <t>3483-12-CM25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -707,12 +707,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>sep-2025</t>
+          <t>ene-2025</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-01-23</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -722,12 +722,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>61.979.020-0</t>
+          <t>65.286.830-4</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>15812.72</v>
+        <v>388.86</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1606-502-CM25</t>
+          <t>1079596-5-CM25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>ene-2025</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-01-31</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>60.108.000-1</t>
+          <t>60.505.101-4</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>AGENCIA CHILENA DE COOPERACION INTERNACIONAL PARA EL DESARROLLO</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -813,13 +813,13 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>839.26</v>
+        <v>21177.67</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1079596-334-CM25</t>
+          <t>1079596-6-CM25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -829,12 +829,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-02-04</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XV ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -874,13 +874,13 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>21699.81</v>
+        <v>23674.93</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>3459-303-CM25</t>
+          <t>3459-2-CM25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -890,12 +890,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-02-04</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -910,7 +910,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -935,13 +935,13 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>3067.45</v>
+        <v>5065.24</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>5360-424-CM25</t>
+          <t>707409-20-CM25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -951,27 +951,27 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-02-19</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>70.770.800-k</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -996,13 +996,13 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>2773.35</v>
+        <v>1786.41</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>521473-22-CM25</t>
+          <t>5360-71-CM25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1012,12 +1012,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-02-20</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1057,13 +1057,13 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>47195.17</v>
+        <v>9514.84</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>635-4846-CM25</t>
+          <t>1079596-30-CM25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1073,12 +1073,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-03-04</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>61.606.000-7</t>
+          <t>60.505.101-4</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DE ARICA Y PARINACOTA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1118,13 +1118,13 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>47374.54</v>
+        <v>21039.62</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>696027-107-CM25</t>
+          <t>3483-42-CM25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1134,12 +1134,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-03-07</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1149,12 +1149,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>61.935.400-1</t>
+          <t>65.286.830-4</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>MINISTERIO PUBLICO</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1179,13 +1179,13 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>343.58</v>
+        <v>1926.56</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>696027-106-CM25</t>
+          <t>5702-194-CM25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1195,12 +1195,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-03-21</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1210,12 +1210,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>61.935.400-1</t>
+          <t>61.979.020-0</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>MINISTERIO PUBLICO</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1240,13 +1240,13 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>2254.52</v>
+        <v>7183.25</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>5360-435-CM25</t>
+          <t>5702-190-CM25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1256,27 +1256,27 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-03-21</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>70.770.800-k</t>
+          <t>61.979.020-0</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1301,13 +1301,13 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>18537.48</v>
+        <v>5832.67</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>1079596-389-CM25</t>
+          <t>3483-62-CM25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1332,12 +1332,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>60.505.101-4</t>
+          <t>65.286.830-4</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XV ZONA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1362,13 +1362,13 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>350.05</v>
+        <v>3567.42</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>1079596-385-CM25</t>
+          <t>1079596-66-CM25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1378,12 +1378,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-04-02</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1398,7 +1398,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XV ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1423,13 +1423,13 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>23409.16</v>
+        <v>19911.97</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>3459-313-CM25</t>
+          <t>5360-155-CM25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1439,27 +1439,27 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-04-30</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>65.287.570-K</t>
+          <t>70.770.800-k</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1484,13 +1484,13 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>1696.65</v>
+        <v>15326.06</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>3483-275-CM25</t>
+          <t>1079596-102-CM25</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1515,12 +1515,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>65.286.830-4</t>
+          <t>60.505.101-4</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1545,13 +1545,13 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>3413.57</v>
+        <v>22444.5</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>3483-282-CM25</t>
+          <t>5702-325-CM25</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1561,27 +1561,27 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>65.286.830-4</t>
+          <t>61.979.020-0</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1606,13 +1606,13 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>3246.79</v>
+        <v>72786.7</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>635-5043-CM25</t>
+          <t>3483-118-CM25</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1622,12 +1622,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-05-13</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1637,12 +1637,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>61.606.000-7</t>
+          <t>65.286.830-4</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DE ARICA Y PARINACOTA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1667,13 +1667,13 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>45813.83</v>
+        <v>3718.66</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>1079596-418-CM25</t>
+          <t>635-3428-CM25</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1683,12 +1683,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-05-15</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1698,12 +1698,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>60.505.101-4</t>
+          <t>61.606.000-7</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XV ZONA</t>
+          <t>SERVICIO DE SALUD DE ARICA Y PARINACOTA</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1728,13 +1728,13 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>2463.89</v>
+        <v>5167.36</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>5702-1-CM26</t>
+          <t>3340-152-CM25</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1744,12 +1744,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2025-05-20</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1759,12 +1759,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>61.979.020-0</t>
+          <t>65.286.850-9</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Direc.Reg.Arica y Parinacota</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1789,13 +1789,13 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>16535.09</v>
+        <v>639.66</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>707409-3-CM26</t>
+          <t>1236-89-CM25</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1805,12 +1805,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2025-05-20</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1820,12 +1820,12 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1850,13 +1850,13 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>535.22</v>
+        <v>798.5599999999999</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>576152-1-CM26</t>
+          <t>707409-46-CM25</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1866,27 +1866,27 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>61.002.002-k</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>SERVICIO DE BIENESTAR  DEL  SRCEI</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1911,13 +1911,13 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>15900.34</v>
+        <v>360.85</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>1079596-5-CM26</t>
+          <t>707409-48-CM25</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1927,12 +1927,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>60.505.101-4</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XV ZONA</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1972,13 +1972,13 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>29912.17</v>
+        <v>716.38</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>5702-26-CM26</t>
+          <t>3483-131-CM25</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1988,12 +1988,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2003,12 +2003,12 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>61.979.020-0</t>
+          <t>65.286.830-4</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Direc.Reg.Arica y Parinacota</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2033,13 +2033,13 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>17226.72</v>
+        <v>91.66</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>3483-13-CM26</t>
+          <t>3483-133-CM25</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2049,12 +2049,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2069,7 +2069,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2094,13 +2094,13 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>398.62</v>
+        <v>274.97</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>635-60-CM26</t>
+          <t>3459-183-CM25</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2110,12 +2110,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2125,12 +2125,12 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>61.606.000-7</t>
+          <t>65.287.570-K</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DE ARICA Y PARINACOTA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2155,13 +2155,13 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>46943.28</v>
+        <v>1204.86</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>1079596-19-CM26</t>
+          <t>3483-132-CM25</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>60.505.101-4</t>
+          <t>65.286.830-4</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XV ZONA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2216,13 +2216,13 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>28255.43</v>
+        <v>1156.59</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>3483-3-CM26</t>
+          <t>1079596-129-CM25</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2247,12 +2247,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>65.286.830-4</t>
+          <t>60.505.101-4</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2277,13 +2277,13 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>3454.15</v>
+        <v>21868.85</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>5360-48-CM26</t>
+          <t>5360-194-CM25</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2293,12 +2293,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2338,13 +2338,13 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>11036.37</v>
+        <v>12003.46</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2021-8-CM26</t>
+          <t>1236-94-CM25</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2354,12 +2354,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2369,12 +2369,12 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>61.101.040-0</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Estado Mayor Conjunto</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2392,24 +2392,20 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
+      <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>243421.02</v>
+        <v>607.24</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>635-197-CM26</t>
+          <t>3459-191-CM25</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2419,12 +2415,12 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2434,12 +2430,12 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>61.606.000-7</t>
+          <t>65.287.570-K</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DE ARICA Y PARINACOTA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2464,13 +2460,13 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>50429.35</v>
+        <v>1274.52</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>1079596-30-CM26</t>
+          <t>3348-70-CM25</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2480,12 +2476,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2025-06-06</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2495,12 +2491,12 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>60.505.101-4</t>
+          <t>61.101.082-6</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XV ZONA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2525,13 +2521,13 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>28229.31</v>
+        <v>26988.9</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>3483-52-CM26</t>
+          <t>707409-60-CM25</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2541,12 +2537,12 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2025-06-09</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2556,12 +2552,12 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>65.286.830-4</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2586,13 +2582,13 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>1820.83</v>
+        <v>217.37</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>3483-70-CM26</t>
+          <t>3348-72-CM25</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2602,12 +2598,12 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2025-06-10</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2617,12 +2613,12 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>65.286.830-4</t>
+          <t>61.101.082-6</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2647,13 +2643,13 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>3351.43</v>
+        <v>2080.91</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>3483-64-CM26</t>
+          <t>635-3620-CM25</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2663,12 +2659,12 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2678,12 +2674,12 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>65.286.830-4</t>
+          <t>61.606.000-7</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>SERVICIO DE SALUD DE ARICA Y PARINACOTA</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2708,13 +2704,13 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>186.6</v>
+        <v>47354.12</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>5360-78-CM26</t>
+          <t>1707-21-CM25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2724,12 +2720,12 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2739,12 +2735,12 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>70.770.800-k</t>
+          <t>60.511.139-4</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE PARINACOTA</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2769,13 +2765,13 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>20186.21</v>
+        <v>618.34</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>707409-32-CM26</t>
+          <t>3459-206-CM25</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2785,12 +2781,12 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2800,12 +2796,12 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>65.287.570-K</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2830,13 +2826,13 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>718.87</v>
+        <v>106.81</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>707409-34-CM26</t>
+          <t>3390-237-CM25</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2846,12 +2842,12 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2861,12 +2857,12 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.962.500-5</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2891,13 +2887,13 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>3599.02</v>
+        <v>427.44</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>1079596-47-CM26</t>
+          <t>1079596-168-CM25</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2907,12 +2903,12 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2927,7 +2923,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XV ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2952,13 +2948,13 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>987.8200000000001</v>
+        <v>23182.09</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>3483-111-CM26</t>
+          <t>3483-151-CM25</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2968,12 +2964,12 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2025-07-03</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2988,7 +2984,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3013,13 +3009,13 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>189.77</v>
+        <v>4317.28</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>1079596-52-CM26</t>
+          <t>3459-211-CM25</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3029,12 +3025,12 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -3044,12 +3040,12 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>60.505.101-4</t>
+          <t>65.287.570-K</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XV ZONA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3074,13 +3070,13 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>25487.53</v>
+        <v>1581.73</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>635-376-CM26</t>
+          <t>5360-268-CM25</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3090,27 +3086,27 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2025-07-15</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>61.606.000-7</t>
+          <t>70.770.800-k</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DE ARICA Y PARINACOTA</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3135,13 +3131,13 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>49296.9</v>
+        <v>24001.66</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>5360-87-CM26</t>
+          <t>5360-269-CM25</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3151,12 +3147,12 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2025-07-15</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -3196,13 +3192,13 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>12519.15</v>
+        <v>12131.89</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>3483-117-CM26</t>
+          <t>635-3800-CM25</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3212,12 +3208,12 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2025-07-22</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -3227,12 +3223,12 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>65.286.830-4</t>
+          <t>61.606.000-7</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>SERVICIO DE SALUD DE ARICA Y PARINACOTA</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3257,13 +3253,13 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>3355.07</v>
+        <v>49732.97</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>3483-166-CM26</t>
+          <t>3483-170-CM25</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3273,12 +3269,12 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2025-07-25</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -3293,7 +3289,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3318,13 +3314,13 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>195.17</v>
+        <v>180.81</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>1079596-71-CM26</t>
+          <t>1079596-195-CM25</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3334,12 +3330,12 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2025-08-04</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -3354,7 +3350,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XV ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3379,13 +3375,13 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>27678.48</v>
+        <v>21872.54</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>3483-170-CM26</t>
+          <t>3390-281-CM25</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3395,12 +3391,12 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -3410,12 +3406,12 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>65.286.830-4</t>
+          <t>61.962.500-5</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -3440,13 +3436,13 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>3913.89</v>
+        <v>3484.31</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>635-553-CM26</t>
+          <t>1337362-48-CM25</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3456,12 +3452,12 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -3471,12 +3467,12 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>61.606.000-7</t>
+          <t>60.905.000-4</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DE ARICA Y PARINACOTA</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -3501,13 +3497,13 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>51231.46</v>
+        <v>1164.75</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>3459-114-CM26</t>
+          <t>635-3949-CM25</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3517,12 +3513,12 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -3532,12 +3528,12 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>65.287.570-K</t>
+          <t>61.606.000-7</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>SERVICIO DE SALUD DE ARICA Y PARINACOTA</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -3562,13 +3558,13 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>337.39</v>
+        <v>46974.55</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>3483-192-CM26</t>
+          <t>3459-257-CM25</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3578,12 +3574,12 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -3593,12 +3589,12 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>65.286.830-4</t>
+          <t>65.287.570-K</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -3623,13 +3619,13 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>390.42</v>
+        <v>175.57</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>635-602-SE26</t>
+          <t>3483-196-CM25</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3639,12 +3635,12 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -3654,12 +3650,12 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>61.606.000-7</t>
+          <t>65.286.830-4</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DE ARICA Y PARINACOTA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -3677,24 +3673,20 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
+      <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>1143688.83</v>
+        <v>177.78</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>1075963-6467-CM26</t>
+          <t>1079596-239-CM25</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3704,12 +3696,12 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2025-09-01</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3719,12 +3711,12 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>60.505.101-4</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3749,13 +3741,13 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>78075.06</v>
+        <v>19791.67</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>1079596-95-CM26</t>
+          <t>3483-200-CM25</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3765,12 +3757,12 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -3780,12 +3772,12 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>60.505.101-4</t>
+          <t>65.286.830-4</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XV ZONA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3810,13 +3802,13 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>29122.13</v>
+        <v>3614.39</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>1075963-6468-CM26</t>
+          <t>707409-93-CM25</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3826,12 +3818,12 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -3841,12 +3833,12 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -3871,13 +3863,13 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>78303.85000000001</v>
+        <v>1537.9</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>941739-43-CM26</t>
+          <t>5702-722-CM25</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3887,27 +3879,27 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>70.770.800-K</t>
+          <t>61.979.020-0</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -3932,13 +3924,13 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>1389.02</v>
+        <v>15812.72</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>1079596-106-CM26</t>
+          <t>1079596-274-CM25</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3948,12 +3940,12 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -3968,7 +3960,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XV ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -3993,13 +3985,13 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>76.06</v>
+        <v>19874.85</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>1337362-34-CM26</t>
+          <t>3483-213-CM25</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4009,12 +4001,12 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -4024,12 +4016,12 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>60.905.000-4</t>
+          <t>65.286.830-4</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>DIRECCIÓN REGIONAL DE ARICA Y PARINACOTA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4054,13 +4046,13 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>1268.08</v>
+        <v>357.44</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>707409-61-CM26</t>
+          <t>1079596-292-CM25</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4070,12 +4062,12 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -4085,12 +4077,12 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>60.505.101-4</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4115,28 +4107,28 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>855.73</v>
+        <v>2986.61</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>1079596-123-CM26</t>
+          <t>635-4452-CM25</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2239-1-LR26</t>
+          <t>2239-13-LR23</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -4146,12 +4138,12 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>60.505.101-4</t>
+          <t>61.606.000-7</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XV ZONA</t>
+          <t>SERVICIO DE SALUD DE ARICA Y PARINACOTA</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -4176,28 +4168,28 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>30455.97</v>
+        <v>45222.53</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>1707-19-CM26</t>
+          <t>5360-378-CM25</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2239-1-LR26</t>
+          <t>2239-13-LR23</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2025-10-10</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -4207,12 +4199,12 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>60.511.139-4</t>
+          <t>70.770.800-k</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE PARINACOTA</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -4237,13 +4229,13 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>614.65</v>
+        <v>12403.66</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>1075963-8976-SE26</t>
+          <t>3483-231-CM25</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4253,12 +4245,12 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -4268,12 +4260,12 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>65.286.830-4</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -4291,39 +4283,35 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
+      <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>742699.71</v>
+        <v>3646.8</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>3348-81-CM26</t>
+          <t>3483-236-CM25</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2239-1-LR26</t>
+          <t>2239-13-LR23</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -4333,12 +4321,12 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>61.101.082-6</t>
+          <t>65.286.830-4</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -4363,28 +4351,28 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>27228.77</v>
+        <v>3648.27</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>5593-115-CM26</t>
+          <t>3390-331-CM25</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2239-1-LR26</t>
+          <t>2239-13-LR23</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -4394,12 +4382,12 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>60.506.000-5</t>
+          <t>61.962.500-5</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -4409,12 +4397,12 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>76.032.107-9</t>
+          <t>96.781.350-8</t>
         </is>
       </c>
       <c r="K65" t="inlineStr"/>
@@ -4424,43 +4412,43 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>10343.8</v>
+        <v>231.33</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>5360-169-CM26</t>
+          <t>635-4664-CM25</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2239-1-LR26</t>
+          <t>2239-13-LR23</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2025-10-29</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>70.770.800-k</t>
+          <t>61.606.000-7</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>SERVICIO DE SALUD DE ARICA Y PARINACOTA</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -4485,43 +4473,43 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>15267.91</v>
+        <v>49699.38</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>1572-76-CM26</t>
+          <t>3459-283-CM25</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2239-1-LR26</t>
+          <t>2239-13-LR23</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>65.287.570-K</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -4546,43 +4534,43 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>35304.47</v>
+        <v>1658.57</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>1572-77-CM26</t>
+          <t>1606-502-CM25</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2239-1-LR26</t>
+          <t>2239-13-LR23</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>60.108.000-1</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>AGENCIA CHILENA DE COOPERACION INTERNACIONAL PARA EL DESARROLLO</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -4607,43 +4595,43 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>1796.58</v>
+        <v>839.26</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>1093870-11-CM26</t>
+          <t>1079596-334-CM25</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2239-1-LR26</t>
+          <t>2239-13-LR23</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>65.184.303-0</t>
+          <t>60.505.101-4</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE EDUCACION SUPERIOR</t>
+          <t>SECCIÓN COMPRAS XV ZONA</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -4668,43 +4656,43 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>852.96</v>
+        <v>21699.81</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>5702-540-CM26</t>
+          <t>3459-303-CM25</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2239-1-LR26</t>
+          <t>2239-13-LR23</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>61.979.020-0</t>
+          <t>65.287.570-K</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Direc.Reg.Arica y Parinacota</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -4729,7 +4717,3923 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
+        <v>3067.45</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>5360-424-CM25</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>nov-2025</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>70.770.800-k</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE TARAPACA</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="n">
+        <v>2773.35</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>521473-22-CM25</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>nov-2025</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>70.770.800-k</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE TARAPACA</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="n">
+        <v>47195.17</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>696027-106-CM25</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>nov-2025</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>2025-11-20</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>61.935.400-1</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>MINISTERIO PUBLICO</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="n">
+        <v>2254.52</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>696027-107-CM25</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>nov-2025</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>2025-11-20</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>61.935.400-1</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>MINISTERIO PUBLICO</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="n">
+        <v>343.58</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>635-4846-CM25</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>nov-2025</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>2025-11-20</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>61.606.000-7</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD DE ARICA Y PARINACOTA</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="n">
+        <v>47374.54</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>5360-435-CM25</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>nov-2025</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>2025-11-25</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>70.770.800-k</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE TARAPACA</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="n">
+        <v>18537.48</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>1079596-385-CM25</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>dic-2025</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>2025-12-01</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>60.505.101-4</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>SECCIÓN COMPRAS XV ZONA</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="n">
+        <v>23409.16</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>1079596-389-CM25</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>dic-2025</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>2025-12-01</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>60.505.101-4</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>SECCIÓN COMPRAS XV ZONA</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="n">
+        <v>350.05</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>3459-313-CM25</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>dic-2025</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>65.287.570-K</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Ejercito de Chile</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="n">
+        <v>1696.65</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>3483-275-CM25</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>dic-2025</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>2025-12-10</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>65.286.830-4</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Ejercito de Chile</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="n">
+        <v>3413.57</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>3483-282-CM25</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>dic-2025</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>65.286.830-4</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Ejercito de Chile</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="n">
+        <v>3246.79</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>635-5043-CM25</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>dic-2025</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>61.606.000-7</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD DE ARICA Y PARINACOTA</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="n">
+        <v>45813.83</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>1079596-418-CM25</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>dic-2025</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>2025-12-23</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>60.505.101-4</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>SECCIÓN COMPRAS XV ZONA</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="n">
+        <v>2463.89</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>5702-1-CM26</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>ene-2026</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>2026-01-02</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>61.979.020-0</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Direc.Reg.Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="n">
+        <v>16535.09</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>707409-3-CM26</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>ene-2026</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>2026-01-07</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>70.574.900-0</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="n">
+        <v>535.22</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>576152-1-CM26</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>ene-2026</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>61.002.002-k</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>SERVICIO DE BIENESTAR  DEL  SRCEI</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="n">
+        <v>15900.34</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>1079596-5-CM26</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>ene-2026</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>2026-01-21</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>60.505.101-4</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>SECCIÓN COMPRAS XV ZONA</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="n">
+        <v>29912.17</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>5702-26-CM26</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>ene-2026</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>2026-01-26</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>61.979.020-0</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Direc.Reg.Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="n">
+        <v>17226.72</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>3483-13-CM26</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>ene-2026</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>2026-01-27</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>65.286.830-4</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Ejercito de Chile</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="n">
+        <v>398.62</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>635-60-CM26</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>ene-2026</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>2026-01-28</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>61.606.000-7</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD DE ARICA Y PARINACOTA</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="n">
+        <v>46943.28</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>1079596-19-CM26</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>feb-2026</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>60.505.101-4</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>SECCIÓN COMPRAS XV ZONA</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr"/>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="n">
+        <v>28255.43</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>3483-3-CM26</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>feb-2026</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>2026-02-03</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>65.286.830-4</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Ejercito de Chile</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr"/>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="n">
+        <v>3454.15</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>5360-48-CM26</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>feb-2026</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>2026-02-03</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>70.770.800-k</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE TARAPACA</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr"/>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="n">
+        <v>11036.37</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2021-8-CM26</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>feb-2026</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>61.101.040-0</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Estado Mayor Conjunto</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="n">
+        <v>243421.02</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>635-197-CM26</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>feb-2026</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>61.606.000-7</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD DE ARICA Y PARINACOTA</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="n">
+        <v>50429.35</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>1079596-30-CM26</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>mar-2026</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>60.505.101-4</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>SECCIÓN COMPRAS XV ZONA</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="n">
+        <v>28229.31</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>3483-52-CM26</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>mar-2026</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>65.286.830-4</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Ejercito de Chile</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr"/>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="n">
+        <v>1820.83</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>3483-70-CM26</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>mar-2026</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>65.286.830-4</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Ejercito de Chile</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr"/>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M98" s="2" t="n">
+        <v>3351.43</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>3483-64-CM26</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>mar-2026</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>65.286.830-4</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Ejercito de Chile</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr"/>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="n">
+        <v>186.6</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>5360-78-CM26</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>mar-2026</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>70.770.800-k</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE TARAPACA</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr"/>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M100" s="2" t="n">
+        <v>20186.21</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>707409-32-CM26</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>mar-2026</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>70.574.900-0</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr"/>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M101" s="2" t="n">
+        <v>718.87</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>707409-34-CM26</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>mar-2026</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>70.574.900-0</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr"/>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M102" s="2" t="n">
+        <v>3599.02</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>1079596-47-CM26</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>mar-2026</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>60.505.101-4</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>SECCIÓN COMPRAS XV ZONA</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr"/>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M103" s="2" t="n">
+        <v>987.8200000000001</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>3483-111-CM26</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>65.286.830-4</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Ejercito de Chile</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr"/>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M104" s="2" t="n">
+        <v>189.77</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>1079596-52-CM26</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>60.505.101-4</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>SECCIÓN COMPRAS XV ZONA</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr"/>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M105" s="2" t="n">
+        <v>25487.53</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>635-376-CM26</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>61.606.000-7</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD DE ARICA Y PARINACOTA</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr"/>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M106" s="2" t="n">
+        <v>49296.9</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>5360-87-CM26</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>70.770.800-k</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE TARAPACA</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr"/>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M107" s="2" t="n">
+        <v>12519.15</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>3483-117-CM26</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>65.286.830-4</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Ejercito de Chile</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr"/>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M108" s="2" t="n">
+        <v>3355.07</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>3483-166-CM26</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>65.286.830-4</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Ejercito de Chile</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr"/>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M109" s="2" t="n">
+        <v>195.17</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>1079596-71-CM26</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>60.505.101-4</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>SECCIÓN COMPRAS XV ZONA</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr"/>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M110" s="2" t="n">
+        <v>27678.48</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>3483-170-CM26</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>65.286.830-4</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>Ejercito de Chile</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr"/>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M111" s="2" t="n">
+        <v>3913.89</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>635-553-CM26</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>61.606.000-7</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD DE ARICA Y PARINACOTA</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr"/>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M112" s="2" t="n">
+        <v>51231.46</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>3459-114-CM26</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>65.287.570-K</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>Ejercito de Chile</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr"/>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M113" s="2" t="n">
+        <v>337.39</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>3483-192-CM26</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>65.286.830-4</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>Ejercito de Chile</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr"/>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M114" s="2" t="n">
+        <v>390.42</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>635-602-SE26</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>61.606.000-7</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD DE ARICA Y PARINACOTA</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M115" s="2" t="n">
+        <v>1143688.83</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>1075963-6467-CM26</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>61.606.001-5</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr"/>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M116" s="2" t="n">
+        <v>78075.06</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>1079596-95-CM26</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>60.505.101-4</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>SECCIÓN COMPRAS XV ZONA</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr"/>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M117" s="2" t="n">
+        <v>29122.13</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>1075963-6468-CM26</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>61.606.001-5</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr"/>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M118" s="2" t="n">
+        <v>78303.85000000001</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>941739-43-CM26</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>70.770.800-K</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE TARAPACA</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr"/>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M119" s="2" t="n">
+        <v>1389.02</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>1079596-106-CM26</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>60.505.101-4</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>SECCIÓN COMPRAS XV ZONA</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr"/>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M120" s="2" t="n">
+        <v>76.06</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>1337362-34-CM26</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>60.905.000-4</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>DIRECCIÓN REGIONAL DE ARICA Y PARINACOTA</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr"/>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M121" s="2" t="n">
+        <v>1268.08</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>707409-61-CM26</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>70.574.900-0</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr"/>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M122" s="2" t="n">
+        <v>855.73</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>1079596-123-CM26</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>60.505.101-4</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>SECCIÓN COMPRAS XV ZONA</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr"/>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M123" s="2" t="n">
+        <v>30455.97</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>1707-19-CM26</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>60.511.139-4</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE PARINACOTA</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr"/>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M124" s="2" t="n">
+        <v>614.65</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>1075963-8976-SE26</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>61.606.001-5</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M125" s="2" t="n">
+        <v>742699.71</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>3348-81-CM26</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>61.101.082-6</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>Ejercito de Chile</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr"/>
+      <c r="L126" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M126" s="2" t="n">
+        <v>27228.77</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>5593-115-CM26</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>60.506.000-5</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>76.032.107-9</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr"/>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M127" s="2" t="n">
+        <v>10343.8</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>5360-169-CM26</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>70.770.800-k</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE TARAPACA</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr"/>
+      <c r="L128" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M128" s="2" t="n">
+        <v>15267.91</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>1572-76-CM26</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>70.072.600-2</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr"/>
+      <c r="L129" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M129" s="2" t="n">
+        <v>35304.47</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>1572-77-CM26</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>70.072.600-2</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr"/>
+      <c r="L130" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M130" s="2" t="n">
+        <v>1796.58</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>1093870-11-CM26</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>65.184.303-0</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>SUBSECRETARIA DE EDUCACION SUPERIOR</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr"/>
+      <c r="L131" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M131" s="2" t="n">
+        <v>852.96</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>5702-540-CM26</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>61.979.020-0</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>Direc.Reg.Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr"/>
+      <c r="L132" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M132" s="2" t="n">
         <v>432.54</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>1079596-142-CM26</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>60.505.101-4</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr"/>
+      <c r="L133" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M133" s="2" t="n">
+        <v>31039.7</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>4232-76-CM26</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>60.505.101-4</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr"/>
+      <c r="L134" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M134" s="2" t="n">
+        <v>22705.44</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/administracion-y-entrega-de-beneficios/arica-y-parinacota.xlsx
+++ b/docs/oc-regiones/administracion-y-entrega-de-beneficios/arica-y-parinacota.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M134"/>
+  <dimension ref="A1:M136"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -605,7 +605,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>COMANDO DE APOYO A LA FUERZA</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>COMANDO DE APOYO A LA FUERZA</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1734,7 +1734,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>3340-152-CM25</t>
+          <t>1236-89-CM25</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1759,12 +1759,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>65.286.850-9</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1789,13 +1789,13 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>639.66</v>
+        <v>798.5599999999999</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>1236-89-CM25</t>
+          <t>3340-152-CM25</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1820,12 +1820,12 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>65.286.850-9</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1850,7 +1850,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>798.5599999999999</v>
+        <v>639.66</v>
       </c>
     </row>
     <row r="24">
@@ -1978,7 +1978,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>3483-131-CM25</t>
+          <t>3483-133-CM25</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2033,13 +2033,13 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>91.66</v>
+        <v>274.97</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>3483-133-CM25</t>
+          <t>3483-131-CM25</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2094,7 +2094,7 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>274.97</v>
+        <v>91.66</v>
       </c>
     </row>
     <row r="28">
@@ -2222,7 +2222,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>1079596-129-CM25</t>
+          <t>1236-94-CM25</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2247,12 +2247,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>60.505.101-4</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2277,7 +2277,7 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>21868.85</v>
+        <v>607.24</v>
       </c>
     </row>
     <row r="31">
@@ -2344,7 +2344,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>1236-94-CM25</t>
+          <t>1079596-129-CM25</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2369,12 +2369,12 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>60.505.101-4</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2399,7 +2399,7 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>607.24</v>
+        <v>21868.85</v>
       </c>
     </row>
     <row r="33">
@@ -4540,7 +4540,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>1606-502-CM25</t>
+          <t>1079596-334-CM25</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4555,7 +4555,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -4565,12 +4565,12 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>60.108.000-1</t>
+          <t>60.505.101-4</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>AGENCIA CHILENA DE COOPERACION INTERNACIONAL PARA EL DESARROLLO</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -4595,13 +4595,13 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>839.26</v>
+        <v>21699.81</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>1079596-334-CM25</t>
+          <t>3459-303-CM25</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -4626,12 +4626,12 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>60.505.101-4</t>
+          <t>65.287.570-K</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XV ZONA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -4656,13 +4656,13 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>21699.81</v>
+        <v>3067.45</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>3459-303-CM25</t>
+          <t>5360-424-CM25</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4677,22 +4677,22 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>65.287.570-K</t>
+          <t>70.770.800-k</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -4717,13 +4717,13 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>3067.45</v>
+        <v>2773.35</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>5360-424-CM25</t>
+          <t>521473-22-CM25</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4738,7 +4738,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -4778,13 +4778,13 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>2773.35</v>
+        <v>47195.17</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>521473-22-CM25</t>
+          <t>635-4846-CM25</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4799,22 +4799,22 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>70.770.800-k</t>
+          <t>61.606.000-7</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>SERVICIO DE SALUD DE ARICA Y PARINACOTA</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -4839,13 +4839,13 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>47195.17</v>
+        <v>47374.54</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>696027-106-CM25</t>
+          <t>696027-107-CM25</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -4900,13 +4900,13 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>2254.52</v>
+        <v>343.58</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>696027-107-CM25</t>
+          <t>696027-106-CM25</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -4961,13 +4961,13 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>343.58</v>
+        <v>2254.52</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>635-4846-CM25</t>
+          <t>5360-435-CM25</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -4982,22 +4982,22 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>61.606.000-7</t>
+          <t>70.770.800-k</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DE ARICA Y PARINACOTA</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -5022,13 +5022,13 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>47374.54</v>
+        <v>18537.48</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>5360-435-CM25</t>
+          <t>1079596-385-CM25</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -5038,27 +5038,27 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>70.770.800-k</t>
+          <t>60.505.101-4</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -5083,13 +5083,13 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>18537.48</v>
+        <v>23409.16</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>1079596-385-CM25</t>
+          <t>1079596-389-CM25</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -5119,7 +5119,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XV ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -5144,13 +5144,13 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>23409.16</v>
+        <v>350.05</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>1079596-389-CM25</t>
+          <t>3459-313-CM25</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -5165,7 +5165,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -5175,12 +5175,12 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>60.505.101-4</t>
+          <t>65.287.570-K</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XV ZONA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -5205,13 +5205,13 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>350.05</v>
+        <v>1696.65</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>3459-313-CM25</t>
+          <t>3483-275-CM25</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -5226,7 +5226,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -5236,12 +5236,12 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>65.287.570-K</t>
+          <t>65.286.830-4</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -5266,13 +5266,13 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>1696.65</v>
+        <v>3413.57</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>3483-275-CM25</t>
+          <t>3483-282-CM25</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -5287,7 +5287,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -5302,7 +5302,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -5327,13 +5327,13 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>3413.57</v>
+        <v>3246.79</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>3483-282-CM25</t>
+          <t>635-5043-CM25</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -5348,7 +5348,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -5358,12 +5358,12 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>65.286.830-4</t>
+          <t>61.606.000-7</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>SERVICIO DE SALUD DE ARICA Y PARINACOTA</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -5388,13 +5388,13 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>3246.79</v>
+        <v>45813.83</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>635-5043-CM25</t>
+          <t>1079596-418-CM25</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -5409,7 +5409,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -5419,12 +5419,12 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>61.606.000-7</t>
+          <t>60.505.101-4</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DE ARICA Y PARINACOTA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -5449,13 +5449,13 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>45813.83</v>
+        <v>2463.89</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>1079596-418-CM25</t>
+          <t>5702-1-CM26</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -5465,12 +5465,12 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>60.505.101-4</t>
+          <t>61.979.020-0</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XV ZONA</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -5510,13 +5510,13 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>2463.89</v>
+        <v>16535.09</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>5702-1-CM26</t>
+          <t>707409-3-CM26</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -5531,7 +5531,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>61.979.020-0</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Direc.Reg.Arica y Parinacota</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>16535.09</v>
+        <v>535.22</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>707409-3-CM26</t>
+          <t>1079596-5-CM26</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -5592,7 +5592,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -5602,12 +5602,12 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>60.505.101-4</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -5632,13 +5632,13 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>535.22</v>
+        <v>29912.17</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>576152-1-CM26</t>
+          <t>5702-26-CM26</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -5653,22 +5653,22 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>61.002.002-k</t>
+          <t>61.979.020-0</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>SERVICIO DE BIENESTAR  DEL  SRCEI</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -5693,13 +5693,13 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>15900.34</v>
+        <v>17226.72</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>1079596-5-CM26</t>
+          <t>3483-13-CM26</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -5714,7 +5714,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -5724,12 +5724,12 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>60.505.101-4</t>
+          <t>65.286.830-4</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XV ZONA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -5754,13 +5754,13 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>29912.17</v>
+        <v>398.62</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>5702-26-CM26</t>
+          <t>635-60-CM26</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -5775,7 +5775,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>61.979.020-0</t>
+          <t>61.606.000-7</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Direc.Reg.Arica y Parinacota</t>
+          <t>SERVICIO DE SALUD DE ARICA Y PARINACOTA</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -5815,13 +5815,13 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>17226.72</v>
+        <v>46943.28</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>3483-13-CM26</t>
+          <t>1079596-19-CM26</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -5831,12 +5831,12 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -5846,12 +5846,12 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>65.286.830-4</t>
+          <t>60.505.101-4</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -5876,13 +5876,13 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>398.62</v>
+        <v>28255.43</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>635-60-CM26</t>
+          <t>5360-48-CM26</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -5892,27 +5892,27 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>61.606.000-7</t>
+          <t>70.770.800-k</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DE ARICA Y PARINACOTA</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -5937,13 +5937,13 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>46943.28</v>
+        <v>11036.37</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>1079596-19-CM26</t>
+          <t>3483-3-CM26</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -5958,7 +5958,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>60.505.101-4</t>
+          <t>65.286.830-4</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XV ZONA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -5998,13 +5998,13 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>28255.43</v>
+        <v>3454.15</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>3483-3-CM26</t>
+          <t>635-197-CM26</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -6019,7 +6019,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -6029,12 +6029,12 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>65.286.830-4</t>
+          <t>61.606.000-7</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>SERVICIO DE SALUD DE ARICA Y PARINACOTA</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -6059,13 +6059,13 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>3454.15</v>
+        <v>50429.35</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>5360-48-CM26</t>
+          <t>1079596-30-CM26</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -6075,27 +6075,27 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>70.770.800-k</t>
+          <t>60.505.101-4</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>11036.37</v>
+        <v>28229.31</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2021-8-CM26</t>
+          <t>3483-52-CM26</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -6136,12 +6136,12 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>61.101.040-0</t>
+          <t>65.286.830-4</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Estado Mayor Conjunto</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -6174,24 +6174,20 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K94" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+      <c r="K94" t="inlineStr"/>
       <c r="L94" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>243421.02</v>
+        <v>1820.83</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>635-197-CM26</t>
+          <t>3483-70-CM26</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -6201,12 +6197,12 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -6216,12 +6212,12 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>61.606.000-7</t>
+          <t>65.286.830-4</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DE ARICA Y PARINACOTA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -6246,13 +6242,13 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>50429.35</v>
+        <v>3351.43</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>1079596-30-CM26</t>
+          <t>3483-64-CM26</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -6267,7 +6263,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -6277,12 +6273,12 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>60.505.101-4</t>
+          <t>65.286.830-4</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XV ZONA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -6307,13 +6303,13 @@
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>28229.31</v>
+        <v>186.6</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>3483-52-CM26</t>
+          <t>5360-78-CM26</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -6328,22 +6324,22 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>65.286.830-4</t>
+          <t>70.770.800-k</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -6368,13 +6364,13 @@
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>1820.83</v>
+        <v>20186.21</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>3483-70-CM26</t>
+          <t>707409-32-CM26</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -6389,7 +6385,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -6399,12 +6395,12 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>65.286.830-4</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -6429,13 +6425,13 @@
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>3351.43</v>
+        <v>718.87</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>3483-64-CM26</t>
+          <t>707409-34-CM26</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -6450,7 +6446,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -6460,12 +6456,12 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>65.286.830-4</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -6490,13 +6486,13 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>186.6</v>
+        <v>3599.02</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>5360-78-CM26</t>
+          <t>1079596-47-CM26</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -6511,22 +6507,22 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>70.770.800-k</t>
+          <t>60.505.101-4</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -6551,13 +6547,13 @@
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>20186.21</v>
+        <v>987.8200000000001</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>707409-32-CM26</t>
+          <t>3483-111-CM26</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -6567,12 +6563,12 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -6582,12 +6578,12 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>65.286.830-4</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -6612,13 +6608,13 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>718.87</v>
+        <v>189.77</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>707409-34-CM26</t>
+          <t>1079596-52-CM26</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -6628,12 +6624,12 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -6643,12 +6639,12 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>60.505.101-4</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -6673,13 +6669,13 @@
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>3599.02</v>
+        <v>25487.53</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>1079596-47-CM26</t>
+          <t>635-376-CM26</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -6689,12 +6685,12 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -6704,12 +6700,12 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>60.505.101-4</t>
+          <t>61.606.000-7</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XV ZONA</t>
+          <t>SERVICIO DE SALUD DE ARICA Y PARINACOTA</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -6734,13 +6730,13 @@
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>987.8200000000001</v>
+        <v>49296.9</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>3483-111-CM26</t>
+          <t>5360-87-CM26</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -6755,22 +6751,22 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>65.286.830-4</t>
+          <t>70.770.800-k</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -6795,13 +6791,13 @@
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>189.77</v>
+        <v>12519.15</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>1079596-52-CM26</t>
+          <t>3483-117-CM26</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -6816,7 +6812,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -6826,12 +6822,12 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>60.505.101-4</t>
+          <t>65.286.830-4</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XV ZONA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -6856,13 +6852,13 @@
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>25487.53</v>
+        <v>3355.07</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>635-376-CM26</t>
+          <t>3483-166-CM26</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -6877,7 +6873,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -6887,12 +6883,12 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>61.606.000-7</t>
+          <t>65.286.830-4</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DE ARICA Y PARINACOTA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -6917,13 +6913,13 @@
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>49296.9</v>
+        <v>195.17</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>5360-87-CM26</t>
+          <t>1079596-71-CM26</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -6938,22 +6934,22 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>70.770.800-k</t>
+          <t>60.505.101-4</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -6978,13 +6974,13 @@
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>12519.15</v>
+        <v>27678.48</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>3483-117-CM26</t>
+          <t>3483-170-CM26</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -6994,12 +6990,12 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -7014,7 +7010,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -7039,13 +7035,13 @@
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>3355.07</v>
+        <v>3913.89</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>3483-166-CM26</t>
+          <t>635-553-CM26</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -7055,12 +7051,12 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -7070,12 +7066,12 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>65.286.830-4</t>
+          <t>61.606.000-7</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>SERVICIO DE SALUD DE ARICA Y PARINACOTA</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -7100,13 +7096,13 @@
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>195.17</v>
+        <v>51231.46</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>1079596-71-CM26</t>
+          <t>3459-114-CM26</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -7116,12 +7112,12 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -7131,12 +7127,12 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>60.505.101-4</t>
+          <t>65.287.570-K</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XV ZONA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -7161,13 +7157,13 @@
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>27678.48</v>
+        <v>337.39</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>3483-170-CM26</t>
+          <t>3483-192-CM26</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -7182,7 +7178,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -7197,7 +7193,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -7222,13 +7218,13 @@
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>3913.89</v>
+        <v>390.42</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>635-553-CM26</t>
+          <t>635-602-SE26</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -7243,7 +7239,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -7276,20 +7272,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K112" t="inlineStr"/>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L112" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>51231.46</v>
+        <v>1143688.83</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>3459-114-CM26</t>
+          <t>1075963-6467-CM26</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -7304,7 +7304,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -7314,12 +7314,12 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>65.287.570-K</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -7344,13 +7344,13 @@
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>337.39</v>
+        <v>78075.06</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>3483-192-CM26</t>
+          <t>1079596-95-CM26</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -7365,7 +7365,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -7375,12 +7375,12 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>65.286.830-4</t>
+          <t>60.505.101-4</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -7405,13 +7405,13 @@
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>390.42</v>
+        <v>29122.13</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>635-602-SE26</t>
+          <t>1075963-6468-CM26</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -7421,12 +7421,12 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -7436,12 +7436,12 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>61.606.000-7</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DE ARICA Y PARINACOTA</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -7459,24 +7459,20 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K115" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+      <c r="K115" t="inlineStr"/>
       <c r="L115" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>1143688.83</v>
+        <v>78303.85000000001</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>1075963-6467-CM26</t>
+          <t>941739-43-CM26</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -7486,27 +7482,27 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>70.770.800-K</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -7531,13 +7527,13 @@
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>78075.06</v>
+        <v>1389.02</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>1079596-95-CM26</t>
+          <t>1079596-106-CM26</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -7547,12 +7543,12 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -7567,7 +7563,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XV ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -7592,13 +7588,13 @@
         </is>
       </c>
       <c r="M117" s="2" t="n">
-        <v>29122.13</v>
+        <v>76.06</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>1075963-6468-CM26</t>
+          <t>1337362-34-CM26</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -7613,7 +7609,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -7623,12 +7619,12 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>60.905.000-4</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -7653,13 +7649,13 @@
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>78303.85000000001</v>
+        <v>1268.08</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>941739-43-CM26</t>
+          <t>707409-61-CM26</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -7674,22 +7670,22 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>70.770.800-K</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -7714,28 +7710,28 @@
         </is>
       </c>
       <c r="M119" s="2" t="n">
-        <v>1389.02</v>
+        <v>855.73</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>1079596-106-CM26</t>
+          <t>1079596-123-CM26</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>2239-13-LR23</t>
+          <t>2239-1-LR26</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -7750,7 +7746,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XV ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -7775,43 +7771,43 @@
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>76.06</v>
+        <v>30455.97</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>1337362-34-CM26</t>
+          <t>1707-19-CM26</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>2239-13-LR23</t>
+          <t>2239-1-LR26</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>60.905.000-4</t>
+          <t>60.511.139-4</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>DIRECCIÓN REGIONAL DE ARICA Y PARINACOTA</t>
+          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE PARINACOTA</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -7836,13 +7832,13 @@
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>1268.08</v>
+        <v>614.65</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>707409-61-CM26</t>
+          <t>1075963-8976-SE26</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -7852,12 +7848,12 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -7867,12 +7863,12 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -7890,20 +7886,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K122" t="inlineStr"/>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L122" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>855.73</v>
+        <v>742699.71</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>1079596-123-CM26</t>
+          <t>5593-115-CM26</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -7918,7 +7918,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -7928,12 +7928,12 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>60.505.101-4</t>
+          <t>60.506.000-5</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XV ZONA</t>
+          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -7943,12 +7943,12 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>96.781.350-8</t>
+          <t>76.032.107-9</t>
         </is>
       </c>
       <c r="K123" t="inlineStr"/>
@@ -7958,13 +7958,13 @@
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>30455.97</v>
+        <v>10343.8</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>1707-19-CM26</t>
+          <t>3348-81-CM26</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -7979,22 +7979,22 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>60.511.139-4</t>
+          <t>61.101.082-6</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE PARINACOTA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -8019,18 +8019,18 @@
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>614.65</v>
+        <v>27228.77</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>1075963-8976-SE26</t>
+          <t>5360-169-CM26</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>2239-13-LR23</t>
+          <t>2239-1-LR26</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -8040,22 +8040,22 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>70.770.800-k</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -8073,24 +8073,20 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K125" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+      <c r="K125" t="inlineStr"/>
       <c r="L125" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M125" s="2" t="n">
-        <v>742699.71</v>
+        <v>15267.91</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>3348-81-CM26</t>
+          <t>1572-76-CM26</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -8105,7 +8101,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -8115,12 +8111,12 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>61.101.082-6</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -8145,13 +8141,13 @@
         </is>
       </c>
       <c r="M126" s="2" t="n">
-        <v>27228.77</v>
+        <v>35304.47</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>5593-115-CM26</t>
+          <t>1572-77-CM26</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -8166,7 +8162,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -8176,12 +8172,12 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>60.506.000-5</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -8191,12 +8187,12 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>76.032.107-9</t>
+          <t>96.781.350-8</t>
         </is>
       </c>
       <c r="K127" t="inlineStr"/>
@@ -8206,13 +8202,13 @@
         </is>
       </c>
       <c r="M127" s="2" t="n">
-        <v>10343.8</v>
+        <v>1796.58</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>5360-169-CM26</t>
+          <t>5702-540-CM26</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -8227,7 +8223,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -8237,12 +8233,12 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>70.770.800-k</t>
+          <t>61.979.020-0</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -8267,13 +8263,13 @@
         </is>
       </c>
       <c r="M128" s="2" t="n">
-        <v>15267.91</v>
+        <v>432.54</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>1572-76-CM26</t>
+          <t>1079596-142-CM26</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -8283,27 +8279,27 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>ago-2026</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>60.505.101-4</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -8328,13 +8324,13 @@
         </is>
       </c>
       <c r="M129" s="2" t="n">
-        <v>35304.47</v>
+        <v>31039.7</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>1572-77-CM26</t>
+          <t>4232-76-CM26</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -8344,27 +8340,27 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>ago-2026</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>60.505.101-4</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -8389,13 +8385,13 @@
         </is>
       </c>
       <c r="M130" s="2" t="n">
-        <v>1796.58</v>
+        <v>22705.44</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>1093870-11-CM26</t>
+          <t>1079596-168-CM26</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -8405,27 +8401,27 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>sep-2026</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>65.184.303-0</t>
+          <t>60.505.101-4</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE EDUCACION SUPERIOR</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -8450,13 +8446,13 @@
         </is>
       </c>
       <c r="M131" s="2" t="n">
-        <v>852.96</v>
+        <v>27895.99</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>5702-540-CM26</t>
+          <t>3459-226-CM26</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -8466,27 +8462,27 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>sep-2026</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>61.979.020-0</t>
+          <t>65.287.570-K</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Direc.Reg.Arica y Parinacota</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -8511,13 +8507,13 @@
         </is>
       </c>
       <c r="M132" s="2" t="n">
-        <v>432.54</v>
+        <v>428.1</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>1079596-142-CM26</t>
+          <t>1079596-179-CM26</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -8527,12 +8523,12 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>sep-2026</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -8572,13 +8568,13 @@
         </is>
       </c>
       <c r="M133" s="2" t="n">
-        <v>31039.7</v>
+        <v>2137.87</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>4232-76-CM26</t>
+          <t>3483-316-CM26</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -8588,27 +8584,27 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>sep-2026</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>60.505.101-4</t>
+          <t>65.286.830-4</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -8633,7 +8629,129 @@
         </is>
       </c>
       <c r="M134" s="2" t="n">
-        <v>22705.44</v>
+        <v>400.66</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>5702-694-CM26</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>61.979.020-0</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr"/>
+      <c r="L135" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M135" s="2" t="n">
+        <v>1353.56</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>4232-88-CM26</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>60.505.101-4</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr"/>
+      <c r="L136" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M136" s="2" t="n">
+        <v>22947.39</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/administracion-y-entrega-de-beneficios/arica-y-parinacota.xlsx
+++ b/docs/oc-regiones/administracion-y-entrega-de-beneficios/arica-y-parinacota.xlsx
@@ -562,7 +562,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -623,7 +627,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -684,7 +692,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -745,7 +757,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -806,7 +822,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -867,7 +887,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -928,7 +952,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -989,7 +1017,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1050,7 +1082,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1111,7 +1147,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1172,7 +1212,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1233,7 +1277,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1294,7 +1342,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1355,7 +1407,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1416,7 +1472,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1477,7 +1537,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1538,7 +1602,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1599,7 +1667,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1660,7 +1732,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1721,7 +1797,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1782,7 +1862,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1843,7 +1927,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1904,7 +1992,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1965,7 +2057,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2026,7 +2122,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2087,7 +2187,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2148,7 +2252,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2209,7 +2317,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2270,7 +2382,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2331,7 +2447,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2392,7 +2512,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2453,7 +2577,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2514,7 +2642,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2575,7 +2707,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2636,7 +2772,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2697,7 +2837,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2758,7 +2902,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2819,7 +2967,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2880,7 +3032,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2941,7 +3097,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3002,7 +3162,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3063,7 +3227,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3124,7 +3292,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3185,7 +3357,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L45" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3246,7 +3422,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L46" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3307,7 +3487,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3368,7 +3552,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L48" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3429,7 +3617,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3490,7 +3682,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L50" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3551,7 +3747,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L51" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3612,7 +3812,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L52" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3673,7 +3877,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L53" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3734,7 +3942,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L54" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3795,7 +4007,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L55" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3856,7 +4072,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L56" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3917,7 +4137,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L57" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3978,7 +4202,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L58" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4039,7 +4267,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L59" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4100,7 +4332,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L60" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4161,7 +4397,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L61" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4222,7 +4462,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L62" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4283,7 +4527,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L63" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4344,7 +4592,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L64" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4405,7 +4657,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L65" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4466,7 +4722,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L66" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4527,7 +4787,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr"/>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L67" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4588,7 +4852,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L68" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4649,7 +4917,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr"/>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L69" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4710,7 +4982,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr"/>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L70" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4771,7 +5047,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr"/>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L71" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4832,7 +5112,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr"/>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L72" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4893,7 +5177,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr"/>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L73" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4954,7 +5242,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr"/>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L74" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5015,7 +5307,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr"/>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L75" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5076,7 +5372,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr"/>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L76" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5137,7 +5437,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr"/>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L77" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5198,7 +5502,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr"/>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L78" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5259,7 +5567,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr"/>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L79" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5320,7 +5632,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr"/>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L80" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5381,7 +5697,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr"/>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L81" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5442,7 +5762,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr"/>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L82" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5503,7 +5827,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr"/>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L83" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5564,7 +5892,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr"/>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L84" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5625,7 +5957,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr"/>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L85" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5686,7 +6022,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr"/>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L86" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5747,7 +6087,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr"/>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L87" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5808,7 +6152,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr"/>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L88" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5869,7 +6217,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K89" t="inlineStr"/>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L89" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5930,7 +6282,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K90" t="inlineStr"/>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L90" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5991,7 +6347,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr"/>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L91" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6052,7 +6412,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K92" t="inlineStr"/>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L92" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6113,7 +6477,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr"/>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L93" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6174,7 +6542,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K94" t="inlineStr"/>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L94" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6235,7 +6607,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K95" t="inlineStr"/>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L95" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6296,7 +6672,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K96" t="inlineStr"/>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L96" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6357,7 +6737,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K97" t="inlineStr"/>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L97" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6418,7 +6802,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K98" t="inlineStr"/>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L98" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6479,7 +6867,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K99" t="inlineStr"/>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L99" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6540,7 +6932,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K100" t="inlineStr"/>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L100" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6601,7 +6997,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K101" t="inlineStr"/>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L101" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6662,7 +7062,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K102" t="inlineStr"/>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L102" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6723,7 +7127,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K103" t="inlineStr"/>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L103" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6784,7 +7192,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K104" t="inlineStr"/>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L104" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6845,7 +7257,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K105" t="inlineStr"/>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L105" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6906,7 +7322,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K106" t="inlineStr"/>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L106" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6967,7 +7387,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K107" t="inlineStr"/>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L107" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7028,7 +7452,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K108" t="inlineStr"/>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L108" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7089,7 +7517,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K109" t="inlineStr"/>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L109" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7150,7 +7582,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K110" t="inlineStr"/>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L110" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7211,7 +7647,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K111" t="inlineStr"/>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L111" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7337,7 +7777,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K113" t="inlineStr"/>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L113" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7398,7 +7842,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K114" t="inlineStr"/>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L114" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7459,7 +7907,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K115" t="inlineStr"/>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L115" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7520,7 +7972,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K116" t="inlineStr"/>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L116" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7581,7 +8037,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K117" t="inlineStr"/>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L117" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7642,7 +8102,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K118" t="inlineStr"/>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L118" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7703,7 +8167,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K119" t="inlineStr"/>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L119" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7764,7 +8232,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K120" t="inlineStr"/>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L120" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7825,7 +8297,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K121" t="inlineStr"/>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L121" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7951,7 +8427,11 @@
           <t>76.032.107-9</t>
         </is>
       </c>
-      <c r="K123" t="inlineStr"/>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L123" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8012,7 +8492,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K124" t="inlineStr"/>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L124" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8073,7 +8557,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K125" t="inlineStr"/>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L125" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8134,7 +8622,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K126" t="inlineStr"/>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L126" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8195,7 +8687,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K127" t="inlineStr"/>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L127" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8256,7 +8752,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K128" t="inlineStr"/>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L128" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8317,7 +8817,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K129" t="inlineStr"/>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L129" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8378,7 +8882,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K130" t="inlineStr"/>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L130" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8439,7 +8947,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K131" t="inlineStr"/>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L131" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8500,7 +9012,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K132" t="inlineStr"/>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L132" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8561,7 +9077,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K133" t="inlineStr"/>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L133" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8622,7 +9142,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K134" t="inlineStr"/>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L134" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8683,7 +9207,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K135" t="inlineStr"/>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L135" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8744,7 +9272,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K136" t="inlineStr"/>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L136" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-regiones/administracion-y-entrega-de-beneficios/arica-y-parinacota.xlsx
+++ b/docs/oc-regiones/administracion-y-entrega-de-beneficios/arica-y-parinacota.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M136"/>
+  <dimension ref="A1:M141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -839,7 +839,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1079596-6-CM25</t>
+          <t>3459-2-CM25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -864,12 +864,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>60.505.101-4</t>
+          <t>65.287.570-K</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -898,13 +898,13 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>23674.93</v>
+        <v>5065.24</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>3459-2-CM25</t>
+          <t>1079596-6-CM25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>65.287.570-K</t>
+          <t>60.505.101-4</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -963,7 +963,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>5065.24</v>
+        <v>23674.93</v>
       </c>
     </row>
     <row r="9">
@@ -2334,7 +2334,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>1236-94-CM25</t>
+          <t>5360-194-CM25</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2354,17 +2354,17 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>70.770.800-k</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2393,13 +2393,13 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>607.24</v>
+        <v>12003.46</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>5360-194-CM25</t>
+          <t>1236-94-CM25</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2419,17 +2419,17 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>70.770.800-k</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2458,7 +2458,7 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>12003.46</v>
+        <v>607.24</v>
       </c>
     </row>
     <row r="32">
@@ -4284,7 +4284,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>1079596-292-CM25</t>
+          <t>635-4452-CM25</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>60.505.101-4</t>
+          <t>61.606.000-7</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>SERVICIO DE SALUD DE ARICA Y PARINACOTA</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4343,13 +4343,13 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>2986.61</v>
+        <v>45222.53</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>635-4452-CM25</t>
+          <t>1079596-292-CM25</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4374,12 +4374,12 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>61.606.000-7</t>
+          <t>60.505.101-4</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DE ARICA Y PARINACOTA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -4408,7 +4408,7 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>45222.53</v>
+        <v>2986.61</v>
       </c>
     </row>
     <row r="62">
@@ -6234,7 +6234,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>5360-48-CM26</t>
+          <t>3483-3-CM26</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -6254,17 +6254,17 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>70.770.800-k</t>
+          <t>65.286.830-4</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -6293,13 +6293,13 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>11036.37</v>
+        <v>3454.15</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>3483-3-CM26</t>
+          <t>5360-48-CM26</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -6319,17 +6319,17 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>65.286.830-4</t>
+          <t>70.770.800-k</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -6358,7 +6358,7 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>3454.15</v>
+        <v>11036.37</v>
       </c>
     </row>
     <row r="92">
@@ -8054,7 +8054,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>1337362-34-CM26</t>
+          <t>707409-61-CM26</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -8079,12 +8079,12 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>60.905.000-4</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -8113,13 +8113,13 @@
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>1268.08</v>
+        <v>855.73</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>707409-61-CM26</t>
+          <t>1337362-34-CM26</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>60.905.000-4</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -8178,7 +8178,7 @@
         </is>
       </c>
       <c r="M119" s="2" t="n">
-        <v>855.73</v>
+        <v>1268.08</v>
       </c>
     </row>
     <row r="120">
@@ -8379,7 +8379,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>5593-115-CM26</t>
+          <t>3348-81-CM26</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -8404,12 +8404,12 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>60.506.000-5</t>
+          <t>61.101.082-6</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -8419,12 +8419,12 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>76.032.107-9</t>
+          <t>96.781.350-8</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
@@ -8438,13 +8438,13 @@
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>10343.8</v>
+        <v>27228.77</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>3348-81-CM26</t>
+          <t>5593-115-CM26</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -8469,12 +8469,12 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>61.101.082-6</t>
+          <t>60.506.000-5</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>96.781.350-8</t>
+          <t>76.032.107-9</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
@@ -8503,7 +8503,7 @@
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>27228.77</v>
+        <v>10343.8</v>
       </c>
     </row>
     <row r="125">
@@ -8574,7 +8574,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>1572-76-CM26</t>
+          <t>1572-77-CM26</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -8633,13 +8633,13 @@
         </is>
       </c>
       <c r="M126" s="2" t="n">
-        <v>35304.47</v>
+        <v>1796.58</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>1572-77-CM26</t>
+          <t>1572-76-CM26</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -8698,7 +8698,7 @@
         </is>
       </c>
       <c r="M127" s="2" t="n">
-        <v>1796.58</v>
+        <v>35304.47</v>
       </c>
     </row>
     <row r="128">
@@ -9244,7 +9244,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -9284,6 +9284,331 @@
       </c>
       <c r="M136" s="2" t="n">
         <v>22947.39</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>1079596-196-CM26</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>60.505.101-4</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L137" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M137" s="2" t="n">
+        <v>28279.54</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>1079596-199-CM26</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>60.505.101-4</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L138" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M138" s="2" t="n">
+        <v>1453.57</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>1606-355-CM26</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>60.108.000-1</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>AGENCIA CHILENA DE COOPERACION INTERNACIONAL PARA EL DESARROLLO</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L139" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M139" s="2" t="n">
+        <v>946.05</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>1079596-201-CM26</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>60.505.101-4</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>76.032.107-9</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L140" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M140" s="2" t="n">
+        <v>145.16</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>1087-241-CM26</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>61.313.000-4</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>CORP NACIONAL FORESTAL</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>SODEXO SOLUCIONES DE MOTIVACION CHILE S.A.</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>96.556.930-8</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L141" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M141" s="2" t="n">
+        <v>3514.49</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/administracion-y-entrega-de-beneficios/arica-y-parinacota.xlsx
+++ b/docs/oc-regiones/administracion-y-entrega-de-beneficios/arica-y-parinacota.xlsx
@@ -609,7 +609,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>COMANDO DE APOYO A LA FUERZA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -739,7 +739,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>COMANDO DE APOYO A LA FUERZA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
